--- a/output/pdf_financials_xlsx/WHIP.xlsx
+++ b/output/pdf_financials_xlsx/WHIP.xlsx
@@ -2367,10 +2367,10 @@
         <v>0</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.06486699999999999</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.683474</v>
       </c>
     </row>
     <row r="93">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.00111</v>
+        <v>-0.00111</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-2.80432</v>
@@ -3916,7 +3916,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4424,7 +4428,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -6001,7 +6009,7 @@
         </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.00111</v>
+        <v>-0.00111</v>
       </c>
       <c r="G74" s="5" t="n">
         <v>-2.80432</v>

--- a/output/pdf_financials_xlsx/WHIP.xlsx
+++ b/output/pdf_financials_xlsx/WHIP.xlsx
@@ -1138,7 +1138,7 @@
         <v>0.19514</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.001315</v>
       </c>
     </row>
     <row r="35">
@@ -1180,7 +1180,7 @@
         <v>0.19514</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.001315</v>
       </c>
     </row>
     <row r="37">
@@ -1432,7 +1432,7 @@
         <v>0.77015</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.63026</v>
+        <v>1.628945</v>
       </c>
     </row>
     <row r="49">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/pdf_financials_xlsx/WHIP.xlsx
+++ b/output/pdf_financials_xlsx/WHIP.xlsx
@@ -559,13 +559,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.020707</v>
+        <v>0.027201</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.125395</v>
+        <v>0.188992</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.203799</v>
+        <v>0.388802</v>
       </c>
     </row>
     <row r="8">
@@ -628,7 +628,7 @@
         <v>2.815153</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.203799</v>
+        <v>0.388802</v>
       </c>
     </row>
     <row r="11">
@@ -1834,10 +1834,10 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.08684699999999999</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.234427</v>
       </c>
     </row>
     <row r="68">
@@ -2542,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.012413</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.117807</v>
       </c>
     </row>
     <row r="102">
@@ -2647,10 +2647,10 @@
         <v>0</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.20793</v>
+        <v>-0.220343</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>2.216742</v>
+        <v>2.098935</v>
       </c>
     </row>
     <row r="107">
@@ -4724,7 +4724,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -7012,7 +7016,11 @@
           <t>Director fees 10</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -7918,7 +7926,11 @@
           <t>Director fees 6</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -8072,7 +8084,11 @@
           <t>Office expenses</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
